--- a/ig/main/ASS-A24-ModeExercice-TypeActivite-ENREG.xlsx
+++ b/ig/main/ASS-A24-ModeExercice-TypeActivite-ENREG.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>ASS_A24-ModeExercice-TypeActivite-ENREG</t>
+    <t>ASS_A24_ModeExercice_TypeActivite_ENREG</t>
   </si>
   <si>
     <t>Title</t>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t>Experimental</t>
+  </si>
+  <si>
+    <t>false</t>
   </si>
   <si>
     <t>Date</t>
@@ -305,7 +308,9 @@
       <c r="A6" t="s" s="2">
         <v>10</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6" t="s" s="2">
+        <v>9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -319,57 +324,59 @@
       <c r="A8" t="s" s="2">
         <v>13</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" t="s" s="2">
+        <v>14</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2"/>
     </row>
@@ -385,48 +392,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>28</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="E2" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2"/>
     </row>

--- a/ig/main/ASS-A24-ModeExercice-TypeActivite-ENREG.xlsx
+++ b/ig/main/ASS-A24-ModeExercice-TypeActivite-ENREG.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
   <si>
     <t>Property</t>
   </si>
@@ -99,16 +99,22 @@
     <t>Source</t>
   </si>
   <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J117-ModeExercice-ENREG/FHIR/JDV-J117-ModeExercice-ENREG</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J119-TypeActiviteLiberale-ENREG/FHIR/JDV-J119-TypeActiviteLiberale-ENREG</t>
+  </si>
+  <si>
     <t>Display</t>
   </si>
   <si>
     <t>Relationship</t>
   </si>
   <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J117-ModeExercice-ENREG/FHIR/JDV-J117-ModeExercice-ENREG</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R23-ModeExercice/FHIR/TRE-R23-ModeExercice</t>
   </si>
   <si>
     <t/>
@@ -257,7 +263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -379,6 +385,22 @@
         <v>26</v>
       </c>
       <c r="B15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -395,45 +417,45 @@
         <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>32</v>
+      </c>
+      <c r="D1" t="s" s="1">
         <v>29</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>30</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E3" s="2"/>
     </row>
